--- a/50_Threshold_OUTPUT_REPORT/50_observation_roc_evaluations.xlsx
+++ b/50_Threshold_OUTPUT_REPORT/50_observation_roc_evaluations.xlsx
@@ -485,7 +485,7 @@
         <v>0.8554578168732507</v>
       </c>
       <c r="E2" t="n">
-        <v>0.272890843662535</v>
+        <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.0645741703318673</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>0.9940023990403839</v>
@@ -1937,7 +1937,7 @@
         <v>0.9984006397441023</v>
       </c>
       <c r="E46" t="n">
-        <v>0.01439424230307873</v>
+        <v>0</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>0.9950019992003198</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0001999200319872108</v>
+        <v>0</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>0.9928028788484606</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1259496201519392</v>
+        <v>0</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.0177928828468612</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
         <v>0.9984006397441023</v>
